--- a/delivery/paid-products/ithalat-depo-teslim-rafa-gelen-net-birim-maliyet/current.xlsx
+++ b/delivery/paid-products/ithalat-depo-teslim-rafa-gelen-net-birim-maliyet/current.xlsx
@@ -1576,6 +1576,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="A12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
@@ -1767,6 +1965,204 @@
                 <xdr:colOff>29</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1972,6 +2368,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="D6" authorId="0">
       <text>
         <r>
@@ -2163,6 +2757,204 @@
                 <xdr:colOff>29</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2368,6 +3160,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="F6" authorId="0">
       <text>
         <r>
@@ -2559,6 +3549,204 @@
                 <xdr:colOff>29</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2764,6 +3952,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="H6" authorId="0">
       <text>
         <r>
@@ -2955,6 +4341,204 @@
                 <xdr:colOff>29</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3160,6 +4744,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="I12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="I13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="I14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="I15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="I16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="I17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="J6" authorId="0">
       <text>
         <r>
@@ -3351,6 +5133,204 @@
                 <xdr:colOff>29</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3566,6 +5546,138 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="A12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
@@ -3764,6 +5876,138 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="C6" authorId="0">
       <text>
         <r>
@@ -3864,6 +6108,204 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="C9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5911,7 +8353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="373">
   <si>
     <t xml:space="preserve">İTHALAT DEPO TESLİM (RAFA GELEN) NET BİRİM MALİYET</t>
   </si>
@@ -6078,6 +8520,33 @@
     <t xml:space="preserve">Endüstriyel Motor</t>
   </si>
   <si>
+    <t xml:space="preserve">Rulman Yatağı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayış Kasnak Seti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pnömatik Silindir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dişli Kutusu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basınç Sensörü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konveyör Rulosu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kompresör Yedeği</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yağ Filtresi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vergi matrah zinciri: GV=CIF×oran, ÖTV=(CIF+GV)×oran, KDV=(CIF+GV+ÖTV)×oran; yurt içi masraflar FOB payıyla ürünlere dağıtılır.</t>
   </si>
   <si>
@@ -6121,6 +8590,42 @@
   </si>
   <si>
     <t xml:space="preserve">Menşe ve uygunluk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigorta Primi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakliyat sigortası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damga Vergisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyanname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bankacılık ve Döviz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ödeme masrafları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konteyner Depolama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bekleme süresi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palet ve Ambalaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taşıma koruması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geçici Depolama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depo elleçleme</t>
   </si>
   <si>
     <t xml:space="preserve">Masraflar TL olarak girilir; dövizle oluşan masraflar kur uygulanarak TL'ye çevrilip girilmelidir.</t>
@@ -7826,13 +10331,13 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1743000</c:v>
+                  <c:v>5279575</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>706437.9</c:v>
+                  <c:v>2139811.7475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51000</c:v>
+                  <c:v>71200</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7840,11 +10345,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89346846"/>
-        <c:axId val="47465017"/>
+        <c:axId val="94307502"/>
+        <c:axId val="99111304"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89346846"/>
+        <c:axId val="94307502"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7877,7 +10382,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47465017"/>
+        <c:crossAx val="99111304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7885,7 +10390,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47465017"/>
+        <c:axId val="99111304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7928,7 +10433,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89346846"/>
+        <c:crossAx val="94307502"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8280,7 +10785,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,48</c:v>
+                  <c:v>1,47</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8356,13 +10861,13 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1.48455989672978</c:v>
+                  <c:v>1.46878593400037</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.48455989672978</c:v>
+                  <c:v>1.46878593400037</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.48455989672978</c:v>
+                  <c:v>1.46878593400037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8370,11 +10875,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="45289131"/>
-        <c:axId val="67425847"/>
+        <c:axId val="83672248"/>
+        <c:axId val="72010332"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45289131"/>
+        <c:axId val="83672248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8407,7 +10912,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67425847"/>
+        <c:crossAx val="72010332"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8415,7 +10920,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67425847"/>
+        <c:axId val="72010332"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8458,7 +10963,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45289131"/>
+        <c:crossAx val="83672248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8600,10 +11105,10 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>15241.0486097892</c:v>
+                  <c:v>17633.2035335719</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39156.7518361446</c:v>
+                  <c:v>51263.5666684809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8611,11 +11116,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94973970"/>
-        <c:axId val="55784451"/>
+        <c:axId val="22904912"/>
+        <c:axId val="87439356"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94973970"/>
+        <c:axId val="22904912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8648,7 +11153,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55784451"/>
+        <c:crossAx val="87439356"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8656,7 +11161,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55784451"/>
+        <c:axId val="87439356"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8699,7 +11204,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94973970"/>
+        <c:crossAx val="22904912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8841,10 +11346,10 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>258758.79</c:v>
+                  <c:v>775456.54975</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>258758.79</c:v>
+                  <c:v>775456.54975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8852,11 +11357,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="9812982"/>
-        <c:axId val="49579197"/>
+        <c:axId val="7207325"/>
+        <c:axId val="78816913"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9812982"/>
+        <c:axId val="7207325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8889,7 +11394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49579197"/>
+        <c:crossAx val="78816913"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8897,7 +11402,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49579197"/>
+        <c:axId val="78816913"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8940,7 +11445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9812982"/>
+        <c:crossAx val="7207325"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9085,7 +11590,7 @@
                   <c:v>0.4053</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>706437.9</c:v>
+                  <c:v>2139811.7475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9093,11 +11598,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="35591126"/>
-        <c:axId val="83026723"/>
+        <c:axId val="51636963"/>
+        <c:axId val="22017001"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35591126"/>
+        <c:axId val="51636963"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9130,7 +11635,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83026723"/>
+        <c:crossAx val="22017001"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9138,7 +11643,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83026723"/>
+        <c:axId val="22017001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9181,7 +11686,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35591126"/>
+        <c:crossAx val="51636963"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11104,7 +13609,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11148,12 +13653,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B4" s="30" t="str">
         <f aca="false">firmaUnvani</f>
@@ -11162,16 +13667,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="B5" s="52" t="n">
         <f aca="false">raporTarihi</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B6" s="54" t="str">
         <f aca="false">KararSonuc</f>
@@ -11180,30 +13685,30 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">ToplamDepoTeslimMaliyeti</f>
-        <v>2587587.9</v>
+        <v>7754565.4975</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">MaliyetFaktoru</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">VergiYukOrani</f>
@@ -11212,34 +13717,34 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">ToplamFOB</f>
-        <v>1743000</v>
+        <v>5279575</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">ToplamVergi</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">ToplamYurtIciMasraf</f>
-        <v>51000</v>
+        <v>71200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">VeriKaliteSkoru</f>
@@ -11248,11 +13753,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">ToplamAdet</f>
-        <v>3275</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11270,85 +13775,85 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="36" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="36" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="36" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -11358,7 +13863,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -11430,7 +13935,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11464,7 +13969,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11629,67 +14134,67 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="56" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B16" s="48" t="n">
         <v>25000</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="56" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B17" s="48" t="n">
         <v>8000</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="56" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B18" s="48" t="n">
         <v>15000</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="56" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B19" s="48" t="n">
         <v>3000</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -11762,7 +14267,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11796,29 +14301,29 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="56" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -11849,7 +14354,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11883,15 +14388,15 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11912,25 +14417,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="57" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="57" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="57" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -12008,7 +14513,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -12042,7 +14547,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -12054,7 +14559,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -12066,788 +14571,788 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="B6" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>277</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>279</v>
+      </c>
+      <c r="G6" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>256</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="F6" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="G6" s="61" t="s">
-        <v>233</v>
-      </c>
       <c r="H6" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C7" s="62" t="n">
         <f aca="true">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="E7" s="60" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="F7" s="60" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G7" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H7" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="58" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="C8" s="63" t="n">
         <v>38.5</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="E8" s="60" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="G8" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H8" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="C9" s="63" t="n">
         <v>35</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="E9" s="60" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="F9" s="60" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="G9" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="58" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C10" s="64" t="n">
         <v>0.05</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E10" s="60" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="G10" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H10" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C11" s="64" t="n">
         <v>0.1</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E11" s="60" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="F11" s="60" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="G11" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H11" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="58" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C12" s="64" t="n">
         <v>0.2</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="F12" s="60" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="G12" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H12" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C13" s="64" t="n">
         <v>0.05</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="G13" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="58" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C14" s="64" t="n">
         <v>1E-007</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G14" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H14" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C15" s="64" t="n">
         <v>0.25</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G15" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H15" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C16" s="63" t="n">
         <v>1.8</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="F16" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G16" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H16" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C17" s="63" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E17" s="60" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="F17" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G17" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H17" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C18" s="64" t="n">
         <v>0.05</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G18" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H18" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C19" s="63" t="n">
         <v>90</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E19" s="60" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F19" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G19" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H19" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C20" s="63" t="n">
         <v>70</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E20" s="60" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="F20" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G20" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H20" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="58" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C21" s="63" t="n">
         <v>100</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E21" s="60" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="F21" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G21" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H21" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C22" s="63" t="n">
         <v>20</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E22" s="60" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="F22" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G22" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H22" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="58" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C23" s="63" t="n">
         <v>10</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E23" s="60" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" s="60" t="s">
         <v>307</v>
       </c>
-      <c r="F23" s="60" t="s">
-        <v>286</v>
-      </c>
       <c r="G23" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H23" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C24" s="63" t="n">
         <v>3008</v>
       </c>
       <c r="D24" s="58" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="E24" s="60" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="F24" s="60" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="G24" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H24" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="58" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C25" s="64" t="n">
         <v>0.1</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="F25" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G25" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H25" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="58" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C26" s="64" t="n">
         <v>0.1</v>
       </c>
       <c r="D26" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G26" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H26" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="58" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B27" s="58" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C27" s="64" t="n">
         <v>0.05</v>
       </c>
       <c r="D27" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G27" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H27" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C28" s="64" t="n">
         <v>0.3</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E28" s="60" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G28" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H28" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="58" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B29" s="58" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C29" s="64" t="n">
         <v>0.15</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E29" s="60" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="F29" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G29" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H29" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="58" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C30" s="64" t="n">
         <v>0.9</v>
       </c>
       <c r="D30" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E30" s="60" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="F30" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G30" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H30" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="58" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B31" s="58" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C31" s="64" t="n">
         <v>0.1</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E31" s="60" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="F31" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G31" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H31" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="58" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C32" s="65" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="E32" s="60" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="F32" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G32" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H32" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="58" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B33" s="58" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C33" s="64" t="n">
         <v>0.5</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E33" s="60" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F33" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G33" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H33" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="58" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C34" s="64" t="n">
         <v>0.5</v>
       </c>
       <c r="D34" s="58" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="E34" s="60" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="F34" s="60" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G34" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H34" s="61" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -12921,7 +15426,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -12955,12 +15460,12 @@
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -13024,7 +15529,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -13088,7 +15593,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -13152,7 +15657,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -13216,7 +15721,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -13280,7 +15785,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -13344,7 +15849,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -13408,7 +15913,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -13472,7 +15977,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -13536,7 +16041,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -13600,7 +16105,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -13664,7 +16169,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -14560,19 +17065,19 @@
       </c>
       <c r="R6" s="0" t="n">
         <f aca="false">IF(OR($K6="",ToplamFOB=""),"",IFERROR($K6/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
-        <v>6759.03614457831</v>
+        <v>3115.25075408532</v>
       </c>
       <c r="S6" s="0" t="n">
         <f aca="false">IF(OR($M6="",$Q6="",$R6=""),"",IFERROR($M6+$Q6+$R6,0))</f>
-        <v>342933.336144578</v>
+        <v>339289.550754085</v>
       </c>
       <c r="T6" s="0" t="n">
         <f aca="false">IF(OR($S6="",$C6=""),"",IFERROR($S6/MAX(BolumPaydaTaban,$C6),0))</f>
-        <v>6858.66672289157</v>
+        <v>6785.79101508171</v>
       </c>
       <c r="U6" s="0" t="n">
         <f aca="false">IF(OR($S6="",$K6=""),"",IFERROR($S6/MAX(BolumPaydaTaban,$K6),0))</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14636,19 +17141,19 @@
       </c>
       <c r="R7" s="0" t="n">
         <f aca="false">IF(OR($K7="",ToplamFOB=""),"",IFERROR($K7/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
-        <v>3379.51807228916</v>
+        <v>1557.62537704266</v>
       </c>
       <c r="S7" s="0" t="n">
         <f aca="false">IF(OR($M7="",$Q7="",$R7=""),"",IFERROR($M7+$Q7+$R7,0))</f>
-        <v>171466.668072289</v>
+        <v>169644.775377043</v>
       </c>
       <c r="T7" s="0" t="n">
         <f aca="false">IF(OR($S7="",$C7=""),"",IFERROR($S7/MAX(BolumPaydaTaban,$C7),0))</f>
-        <v>857.333340361446</v>
+        <v>848.223876885213</v>
       </c>
       <c r="U7" s="0" t="n">
         <f aca="false">IF(OR($S7="",$K7=""),"",IFERROR($S7/MAX(BolumPaydaTaban,$K7),0))</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14712,19 +17217,19 @@
       </c>
       <c r="R8" s="0" t="n">
         <f aca="false">IF(OR($K8="",ToplamFOB=""),"",IFERROR($K8/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
-        <v>14746.9879518072</v>
+        <v>6796.91073618615</v>
       </c>
       <c r="S8" s="0" t="n">
         <f aca="false">IF(OR($M8="",$Q8="",$R8=""),"",IFERROR($M8+$Q8+$R8,0))</f>
-        <v>748218.187951807</v>
+        <v>740268.110736186</v>
       </c>
       <c r="T8" s="0" t="n">
         <f aca="false">IF(OR($S8="",$C8=""),"",IFERROR($S8/MAX(BolumPaydaTaban,$C8),0))</f>
-        <v>249.406062650602</v>
+        <v>246.756036912062</v>
       </c>
       <c r="U8" s="0" t="n">
         <f aca="false">IF(OR($S8="",$K8=""),"",IFERROR($S8/MAX(BolumPaydaTaban,$K8),0))</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14788,116 +17293,628 @@
       </c>
       <c r="R9" s="0" t="n">
         <f aca="false">IF(OR($K9="",ToplamFOB=""),"",IFERROR($K9/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
-        <v>26114.4578313253</v>
+        <v>12036.1960953296</v>
       </c>
       <c r="S9" s="0" t="n">
         <f aca="false">IF(OR($M9="",$Q9="",$R9=""),"",IFERROR($M9+$Q9+$R9,0))</f>
-        <v>1324969.70783133</v>
+        <v>1310891.44609533</v>
       </c>
       <c r="T9" s="0" t="n">
         <f aca="false">IF(OR($S9="",$C9=""),"",IFERROR($S9/MAX(BolumPaydaTaban,$C9),0))</f>
-        <v>52998.788313253</v>
+        <v>52435.6578438132</v>
       </c>
       <c r="U9" s="0" t="n">
         <f aca="false">IF(OR($S9="",$K9=""),"",IFERROR($S9/MAX(BolumPaydaTaban,$K9),0))</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
+      <c r="A10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <f aca="false">IF(OR($C10="",$D10="",$F10=""),"",IFERROR($C10*$D10*$F10,0))</f>
+        <v>277200</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <f aca="false">IF(OR($K10="",$G10=""),"",IFERROR($K10*$G10,0))</f>
+        <v>13860</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <f aca="false">IF(OR($K10="",$L10=""),"",IFERROR($K10+$L10,0))</f>
+        <v>291060</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <f aca="false">IF(OR($M10="",$H10=""),"",IFERROR($M10*$H10,0))</f>
+        <v>14553</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <f aca="false">IF(OR($M10="",$N10="",$I10=""),"",IFERROR(($M10+$N10)*$I10,0))</f>
+        <v>30561.3</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <f aca="false">IF(OR($M10="",$N10="",$O10="",$J10=""),"",IFERROR(($M10+$N10+$O10)*$J10,0))</f>
+        <v>67234.86</v>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <f aca="false">IF(OR($N10="",$O10="",$P10=""),"",IFERROR($N10+$O10+$P10,0))</f>
+        <v>112349.16</v>
+      </c>
+      <c r="R10" s="0" t="n">
+        <f aca="false">IF(OR($K10="",ToplamFOB=""),"",IFERROR($K10/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>3738.30090490238</v>
+      </c>
+      <c r="S10" s="0" t="n">
+        <f aca="false">IF(OR($M10="",$Q10="",$R10=""),"",IFERROR($M10+$Q10+$R10,0))</f>
+        <v>407147.460904902</v>
+      </c>
+      <c r="T10" s="0" t="n">
+        <f aca="false">IF(OR($S10="",$C10=""),"",IFERROR($S10/MAX(BolumPaydaTaban,$C10),0))</f>
+        <v>1017.86865226226</v>
+      </c>
+      <c r="U10" s="0" t="n">
+        <f aca="false">IF(OR($S10="",$K10=""),"",IFERROR($S10/MAX(BolumPaydaTaban,$K10),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
+      <c r="A11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <f aca="false">IF(OR($C11="",$D11="",$F11=""),"",IFERROR($C11*$D11*$F11,0))</f>
+        <v>259875</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">IF(OR($K11="",$G11=""),"",IFERROR($K11*$G11,0))</f>
+        <v>12993.75</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <f aca="false">IF(OR($K11="",$L11=""),"",IFERROR($K11+$L11,0))</f>
+        <v>272868.75</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <f aca="false">IF(OR($M11="",$H11=""),"",IFERROR($M11*$H11,0))</f>
+        <v>13643.4375</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <f aca="false">IF(OR($M11="",$N11="",$I11=""),"",IFERROR(($M11+$N11)*$I11,0))</f>
+        <v>28651.21875</v>
+      </c>
+      <c r="P11" s="0" t="n">
+        <f aca="false">IF(OR($M11="",$N11="",$O11="",$J11=""),"",IFERROR(($M11+$N11+$O11)*$J11,0))</f>
+        <v>63032.68125</v>
+      </c>
+      <c r="Q11" s="0" t="n">
+        <f aca="false">IF(OR($N11="",$O11="",$P11=""),"",IFERROR($N11+$O11+$P11,0))</f>
+        <v>105327.3375</v>
+      </c>
+      <c r="R11" s="0" t="n">
+        <f aca="false">IF(OR($K11="",ToplamFOB=""),"",IFERROR($K11/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>3504.65709834598</v>
+      </c>
+      <c r="S11" s="0" t="n">
+        <f aca="false">IF(OR($M11="",$Q11="",$R11=""),"",IFERROR($M11+$Q11+$R11,0))</f>
+        <v>381700.744598346</v>
+      </c>
+      <c r="T11" s="0" t="n">
+        <f aca="false">IF(OR($S11="",$C11=""),"",IFERROR($S11/MAX(BolumPaydaTaban,$C11),0))</f>
+        <v>2544.67163065564</v>
+      </c>
+      <c r="U11" s="0" t="n">
+        <f aca="false">IF(OR($S11="",$K11=""),"",IFERROR($S11/MAX(BolumPaydaTaban,$K11),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
+      <c r="A12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>260</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <f aca="false">IF(OR($C12="",$D12="",$F12=""),"",IFERROR($C12*$D12*$F12,0))</f>
+        <v>800800</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">IF(OR($K12="",$G12=""),"",IFERROR($K12*$G12,0))</f>
+        <v>40040</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <f aca="false">IF(OR($K12="",$L12=""),"",IFERROR($K12+$L12,0))</f>
+        <v>840840</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <f aca="false">IF(OR($M12="",$H12=""),"",IFERROR($M12*$H12,0))</f>
+        <v>42042</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <f aca="false">IF(OR($M12="",$N12="",$I12=""),"",IFERROR(($M12+$N12)*$I12,0))</f>
+        <v>88288.2</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <f aca="false">IF(OR($M12="",$N12="",$O12="",$J12=""),"",IFERROR(($M12+$N12+$O12)*$J12,0))</f>
+        <v>194234.04</v>
+      </c>
+      <c r="Q12" s="0" t="n">
+        <f aca="false">IF(OR($N12="",$O12="",$P12=""),"",IFERROR($N12+$O12+$P12,0))</f>
+        <v>324564.24</v>
+      </c>
+      <c r="R12" s="0" t="n">
+        <f aca="false">IF(OR($K12="",ToplamFOB=""),"",IFERROR($K12/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>10799.5359474958</v>
+      </c>
+      <c r="S12" s="0" t="n">
+        <f aca="false">IF(OR($M12="",$Q12="",$R12=""),"",IFERROR($M12+$Q12+$R12,0))</f>
+        <v>1176203.7759475</v>
+      </c>
+      <c r="T12" s="0" t="n">
+        <f aca="false">IF(OR($S12="",$C12=""),"",IFERROR($S12/MAX(BolumPaydaTaban,$C12),0))</f>
+        <v>14702.5471993437</v>
+      </c>
+      <c r="U12" s="0" t="n">
+        <f aca="false">IF(OR($S12="",$K12=""),"",IFERROR($S12/MAX(BolumPaydaTaban,$K12),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="A13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <f aca="false">IF(OR($C13="",$D13="",$F13=""),"",IFERROR($C13*$D13*$F13,0))</f>
+        <v>730800</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <f aca="false">IF(OR($K13="",$G13=""),"",IFERROR($K13*$G13,0))</f>
+        <v>36540</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <f aca="false">IF(OR($K13="",$L13=""),"",IFERROR($K13+$L13,0))</f>
+        <v>767340</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <f aca="false">IF(OR($M13="",$H13=""),"",IFERROR($M13*$H13,0))</f>
+        <v>38367</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <f aca="false">IF(OR($M13="",$N13="",$I13=""),"",IFERROR(($M13+$N13)*$I13,0))</f>
+        <v>80570.7</v>
+      </c>
+      <c r="P13" s="0" t="n">
+        <f aca="false">IF(OR($M13="",$N13="",$O13="",$J13=""),"",IFERROR(($M13+$N13+$O13)*$J13,0))</f>
+        <v>177255.54</v>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <f aca="false">IF(OR($N13="",$O13="",$P13=""),"",IFERROR($N13+$O13+$P13,0))</f>
+        <v>296193.24</v>
+      </c>
+      <c r="R13" s="0" t="n">
+        <f aca="false">IF(OR($K13="",ToplamFOB=""),"",IFERROR($K13/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>9855.52056746992</v>
+      </c>
+      <c r="S13" s="0" t="n">
+        <f aca="false">IF(OR($M13="",$Q13="",$R13=""),"",IFERROR($M13+$Q13+$R13,0))</f>
+        <v>1073388.76056747</v>
+      </c>
+      <c r="T13" s="0" t="n">
+        <f aca="false">IF(OR($S13="",$C13=""),"",IFERROR($S13/MAX(BolumPaydaTaban,$C13),0))</f>
+        <v>89449.0633806225</v>
+      </c>
+      <c r="U13" s="0" t="n">
+        <f aca="false">IF(OR($S13="",$K13=""),"",IFERROR($S13/MAX(BolumPaydaTaban,$K13),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
+      <c r="A14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <f aca="false">IF(OR($C14="",$D14="",$F14=""),"",IFERROR($C14*$D14*$F14,0))</f>
+        <v>403200</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">IF(OR($K14="",$G14=""),"",IFERROR($K14*$G14,0))</f>
+        <v>20160</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <f aca="false">IF(OR($K14="",$L14=""),"",IFERROR($K14+$L14,0))</f>
+        <v>423360</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <f aca="false">IF(OR($M14="",$H14=""),"",IFERROR($M14*$H14,0))</f>
+        <v>21168</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <f aca="false">IF(OR($M14="",$N14="",$I14=""),"",IFERROR(($M14+$N14)*$I14,0))</f>
+        <v>44452.8</v>
+      </c>
+      <c r="P14" s="0" t="n">
+        <f aca="false">IF(OR($M14="",$N14="",$O14="",$J14=""),"",IFERROR(($M14+$N14+$O14)*$J14,0))</f>
+        <v>97796.16</v>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <f aca="false">IF(OR($N14="",$O14="",$P14=""),"",IFERROR($N14+$O14+$P14,0))</f>
+        <v>163416.96</v>
+      </c>
+      <c r="R14" s="0" t="n">
+        <f aca="false">IF(OR($K14="",ToplamFOB=""),"",IFERROR($K14/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>5437.52858894892</v>
+      </c>
+      <c r="S14" s="0" t="n">
+        <f aca="false">IF(OR($M14="",$Q14="",$R14=""),"",IFERROR($M14+$Q14+$R14,0))</f>
+        <v>592214.488588949</v>
+      </c>
+      <c r="T14" s="0" t="n">
+        <f aca="false">IF(OR($S14="",$C14=""),"",IFERROR($S14/MAX(BolumPaydaTaban,$C14),0))</f>
+        <v>1974.0482952965</v>
+      </c>
+      <c r="U14" s="0" t="n">
+        <f aca="false">IF(OR($S14="",$K14=""),"",IFERROR($S14/MAX(BolumPaydaTaban,$K14),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
+      <c r="A15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <f aca="false">IF(OR($C15="",$D15="",$F15=""),"",IFERROR($C15*$D15*$F15,0))</f>
+        <v>207900</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">IF(OR($K15="",$G15=""),"",IFERROR($K15*$G15,0))</f>
+        <v>10395</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <f aca="false">IF(OR($K15="",$L15=""),"",IFERROR($K15+$L15,0))</f>
+        <v>218295</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <f aca="false">IF(OR($M15="",$H15=""),"",IFERROR($M15*$H15,0))</f>
+        <v>10914.75</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <f aca="false">IF(OR($M15="",$N15="",$I15=""),"",IFERROR(($M15+$N15)*$I15,0))</f>
+        <v>22920.975</v>
+      </c>
+      <c r="P15" s="0" t="n">
+        <f aca="false">IF(OR($M15="",$N15="",$O15="",$J15=""),"",IFERROR(($M15+$N15+$O15)*$J15,0))</f>
+        <v>50426.145</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <f aca="false">IF(OR($N15="",$O15="",$P15=""),"",IFERROR($N15+$O15+$P15,0))</f>
+        <v>84261.87</v>
+      </c>
+      <c r="R15" s="0" t="n">
+        <f aca="false">IF(OR($K15="",ToplamFOB=""),"",IFERROR($K15/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>2803.72567867679</v>
+      </c>
+      <c r="S15" s="0" t="n">
+        <f aca="false">IF(OR($M15="",$Q15="",$R15=""),"",IFERROR($M15+$Q15+$R15,0))</f>
+        <v>305360.595678677</v>
+      </c>
+      <c r="T15" s="0" t="n">
+        <f aca="false">IF(OR($S15="",$C15=""),"",IFERROR($S15/MAX(BolumPaydaTaban,$C15),0))</f>
+        <v>508.934326131128</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <f aca="false">IF(OR($S15="",$K15=""),"",IFERROR($S15/MAX(BolumPaydaTaban,$K15),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
+      <c r="A16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>720</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <f aca="false">IF(OR($C16="",$D16="",$F16=""),"",IFERROR($C16*$D16*$F16,0))</f>
+        <v>554400</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">IF(OR($K16="",$G16=""),"",IFERROR($K16*$G16,0))</f>
+        <v>27720</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <f aca="false">IF(OR($K16="",$L16=""),"",IFERROR($K16+$L16,0))</f>
+        <v>582120</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <f aca="false">IF(OR($M16="",$H16=""),"",IFERROR($M16*$H16,0))</f>
+        <v>29106</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <f aca="false">IF(OR($M16="",$N16="",$I16=""),"",IFERROR(($M16+$N16)*$I16,0))</f>
+        <v>61122.6</v>
+      </c>
+      <c r="P16" s="0" t="n">
+        <f aca="false">IF(OR($M16="",$N16="",$O16="",$J16=""),"",IFERROR(($M16+$N16+$O16)*$J16,0))</f>
+        <v>134469.72</v>
+      </c>
+      <c r="Q16" s="0" t="n">
+        <f aca="false">IF(OR($N16="",$O16="",$P16=""),"",IFERROR($N16+$O16+$P16,0))</f>
+        <v>224698.32</v>
+      </c>
+      <c r="R16" s="0" t="n">
+        <f aca="false">IF(OR($K16="",ToplamFOB=""),"",IFERROR($K16/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>7476.60180980477</v>
+      </c>
+      <c r="S16" s="0" t="n">
+        <f aca="false">IF(OR($M16="",$Q16="",$R16=""),"",IFERROR($M16+$Q16+$R16,0))</f>
+        <v>814294.921809805</v>
+      </c>
+      <c r="T16" s="0" t="n">
+        <f aca="false">IF(OR($S16="",$C16=""),"",IFERROR($S16/MAX(BolumPaydaTaban,$C16),0))</f>
+        <v>40714.7460904902</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <f aca="false">IF(OR($S16="",$K16=""),"",IFERROR($S16/MAX(BolumPaydaTaban,$K16),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
+      <c r="A17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <f aca="false">IF(OR($C17="",$D17="",$F17=""),"",IFERROR($C17*$D17*$F17,0))</f>
+        <v>302400</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <f aca="false">IF(OR($K17="",$G17=""),"",IFERROR($K17*$G17,0))</f>
+        <v>15120</v>
+      </c>
+      <c r="M17" s="0" t="n">
+        <f aca="false">IF(OR($K17="",$L17=""),"",IFERROR($K17+$L17,0))</f>
+        <v>317520</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <f aca="false">IF(OR($M17="",$H17=""),"",IFERROR($M17*$H17,0))</f>
+        <v>15876</v>
+      </c>
+      <c r="O17" s="0" t="n">
+        <f aca="false">IF(OR($M17="",$N17="",$I17=""),"",IFERROR(($M17+$N17)*$I17,0))</f>
+        <v>33339.6</v>
+      </c>
+      <c r="P17" s="0" t="n">
+        <f aca="false">IF(OR($M17="",$N17="",$O17="",$J17=""),"",IFERROR(($M17+$N17+$O17)*$J17,0))</f>
+        <v>73347.12</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <f aca="false">IF(OR($N17="",$O17="",$P17=""),"",IFERROR($N17+$O17+$P17,0))</f>
+        <v>122562.72</v>
+      </c>
+      <c r="R17" s="0" t="n">
+        <f aca="false">IF(OR($K17="",ToplamFOB=""),"",IFERROR($K17/MAX(BolumPaydaTaban,ToplamFOB)*ToplamYurtIciMasraf,0))</f>
+        <v>4078.14644171169</v>
+      </c>
+      <c r="S17" s="0" t="n">
+        <f aca="false">IF(OR($M17="",$Q17="",$R17=""),"",IFERROR($M17+$Q17+$R17,0))</f>
+        <v>444160.866441712</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <f aca="false">IF(OR($S17="",$C17=""),"",IFERROR($S17/MAX(BolumPaydaTaban,$C17),0))</f>
+        <v>370.134055368093</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <f aca="false">IF(OR($S17="",$K17=""),"",IFERROR($S17/MAX(BolumPaydaTaban,$K17),0))</f>
+        <v>1.46878593400037</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20"/>
@@ -38745,7 +41762,7 @@
     </row>
     <row r="2006" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2006" s="11" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B2006" s="11"/>
       <c r="C2006" s="11"/>
@@ -38874,7 +41891,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -38908,100 +41925,136 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B6" s="21" t="n">
         <v>25000</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>8000</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>15000</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>3000</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="A11" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="A12" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="A13" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="A14" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
+      <c r="A15" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20"/>
@@ -43950,7 +47003,7 @@
     </row>
     <row r="1006" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1006" s="11" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="B1006" s="11"/>
       <c r="C1006" s="11"/>
@@ -44028,7 +47081,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -44062,125 +47115,125 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">IFERROR(COUNTA(tblUrun[Ürün Adı]),0)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[Adet]),0)</f>
-        <v>3275</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[FOB TL]),0)</f>
-        <v>1743000</v>
+        <v>5279575</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[Navlun ve Sigorta TL]),0)</f>
-        <v>87150</v>
+        <v>263978.75</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[CIF TL]),0)</f>
-        <v>1830150</v>
+        <v>5543553.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[Gümrük Vergisi TL]),0)</f>
-        <v>91507.5</v>
+        <v>277177.6875</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[ÖTV TL]),0)</f>
-        <v>192165.75</v>
+        <v>582073.14375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[KDV TL]),0)</f>
-        <v>422764.65</v>
+        <v>1280560.91625</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[Vergi Toplam TL]),0)</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblMasraf[Tutar TL]),0)</f>
-        <v>51000</v>
+        <v>71200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B17" s="26" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[Depo Teslim Toplam TL]),0)</f>
-        <v>2587587.9</v>
+        <v>7754565.4975</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">IFERROR(AVERAGE(tblUrun[kur]),0)</f>
@@ -44189,25 +47242,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B19" s="26" t="n">
         <f aca="false">IFERROR(AVERAGE(tblUrun[Net Birim Maliyet TL]),0)</f>
-        <v>15241.0486097892</v>
+        <v>17633.2035335719</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B20" s="27" t="n">
         <f aca="false">IFERROR(ToplamDepoTeslimMaliyeti/MAX(BolumPaydaTaban,ToplamFOB),0)</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">IFERROR(ToplamVergi/MAX(BolumPaydaTaban,ToplamCIF),0)</f>
@@ -44216,66 +47269,66 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B22" s="25" t="n">
         <f aca="false">IFERROR(COUNTIF(tblUrun[Net Birim Maliyet TL],"&gt;"&amp;IFERROR(AVERAGE(tblUrun[Net Birim Maliyet TL])+AnomaliZEsik*IFERROR(_xlfn.STDEV.P(tblUrun[Net Birim Maliyet TL]),0),0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">IFERROR(IF(COUNTA(tblUrun[Ürün Adı])=0,0,AnomaliUrunAdedi/COUNTA(tblUrun[Ürün Adı])),0)</f>
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">IFERROR(AVERAGE(tblUrun[Net Birim Maliyet TL]),0)</f>
-        <v>15241.0486097892</v>
+        <v>17633.2035335719</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IFERROR(SLOPE(tblUrun[Depo Teslim Toplam TL],tblUrun[Adet]),0)</f>
-        <v>33.1091678405135</v>
+        <v>-44.4590819391567</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B28" s="28" t="n">
         <f aca="false">IFERROR(IF(SUM(tblUrun[Depo Teslim Toplam TL])=0,0,MAX(tblUrun[Depo Teslim Toplam TL])/SUM(tblUrun[Depo Teslim Toplam TL])),0)</f>
-        <v>0.512048192771084</v>
+        <v>0.169047697968113</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="24" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">IFERROR(ToplamDepoTeslimMaliyeti*(1-OncekiKur/MAX(BolumPaydaTaban,OrtalamaKur)),0)</f>
-        <v>-905655762412412</v>
+        <v>-2714097916370430</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B30" s="26" t="n">
         <f aca="false">IFERROR(ToplamYurtIciMasraf-SUM(tblUrun[Yurt İçi Masraf Payı TL]),0)</f>
@@ -44284,7 +47337,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="24" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B31" s="28" t="n">
         <f aca="false">IFERROR(ToplamVergi/MAX(BolumPaydaTaban,ToplamCIF),0)</f>
@@ -44293,52 +47346,52 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="B32" s="28" t="n">
         <f aca="false">IFERROR(IF(COUNTA(tblUrun[Ürün Adı])=0,0,AnomaliUrunAdedi/COUNTA(tblUrun[Ürün Adı])),0)</f>
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="24" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B33" s="26" t="n">
         <f aca="false">IFERROR(MAX(ABS(SenaryoMaliyetKotumser-SenaryoMaliyetIyimser),ABS(SenaryoVergiKotumser-SenaryoVergiIyimser)),0)</f>
-        <v>517517.58</v>
+        <v>1550913.0995</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="B34" s="26" t="n">
         <f aca="false">IFERROR(SenaryoMaliyetKotumser-SenaryoMaliyetBaz,0)</f>
-        <v>258758.79</v>
+        <v>775456.54975</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="24" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">IFERROR(ToplamDepoTeslimMaliyeti/MAX(BolumPaydaTaban,ToplamFOB),0)</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="24" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B36" s="25" t="n">
         <f aca="false">IFERROR(IF(SUM(tblUrun[FOB TL])=0,0,SUMPRODUCT(tblUrun[FOB TL],tblUrun[FOB TL])/MAX(BolumPaydaTaban,SUM(tblUrun[FOB TL])^2)),0)</f>
-        <v>0.367760197416171</v>
+        <v>0.109119788636602</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="24" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B37" s="25" t="n">
         <f aca="false">VeriKaliteSkoru</f>
@@ -44347,100 +47400,100 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="B38" s="26" t="n">
         <f aca="false">IFERROR(_xlfn.FORECAST.LINEAR(COUNTA(tblUrun[Adet])+1,tblUrun[Depo Teslim Toplam TL],tblUrun[Adet]),0)</f>
-        <v>619954.389669782</v>
+        <v>668002.446532015</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B39" s="26" t="n">
         <f aca="false">IFERROR(_xlfn.PERCENTILE.INC(tblUrun[Net Birim Maliyet TL],P90Kuantil),0)</f>
-        <v>39156.7518361446</v>
+        <v>51263.5666684809</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B40" s="26" t="n">
         <f aca="false">IFERROR(NPV(IskontoOrani,ToplamDepoTeslimMaliyeti),0)</f>
-        <v>2352352.63636364</v>
+        <v>7049604.99772727</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="24" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B41" s="26" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamVergi-PesinOdemeTutari),0)</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="24" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B43" s="26" t="n">
         <f aca="false">modulT1BirimMaliyetOrt</f>
-        <v>15241.0486097892</v>
+        <v>17633.2035335719</v>
       </c>
       <c r="C43" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T1: Ortalama birim maliyet "&amp;TEXT(modulT1BirimMaliyetOrt,"#,##0")&amp;" ₺",IF(modulT1BirimMaliyetOrt&gt;OrtalamaNetBirimMaliyet,"birim maliyet ortalamanın üzerinde","birim maliyet dağılımı normal"))</f>
-        <v>T1: Ortalama birim maliyet 15.241 ₺ | birim maliyet dağılımı normal</v>
+        <v>T1: Ortalama birim maliyet 17.633 ₺ | birim maliyet dağılımı normal</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="24" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B44" s="26" t="n">
         <f aca="false">modulT2MaliyetEgim</f>
-        <v>33.1091678405135</v>
+        <v>-44.4590819391567</v>
       </c>
       <c r="C44" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T2: Maliyet eğimi "&amp;TEXT(modulT2MaliyetEgim,"#,##0")&amp;" ₺/adet",IF(modulT2MaliyetEgim&gt;0,"maliyet adetle artıyor","maliyet adetten bağımsız"))</f>
-        <v>T2: Maliyet eğimi 33 ₺/adet | maliyet adetle artıyor</v>
+        <v>T2: Maliyet eğimi -44 ₺/adet | maliyet adetten bağımsız</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="24" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B45" s="28" t="n">
         <f aca="false">modulT3ParetoPay</f>
-        <v>0.512048192771084</v>
+        <v>0.169047697968113</v>
       </c>
       <c r="C45" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T3: En yüksek maliyetli ürün toplamın %"&amp;TEXT(modulT3ParetoPay*100,"0")&amp;"",IF(modulT3ParetoPay&gt;ParetoEsikOran,"yoğunlaşma yüksek, tek ürüne bağımlılık var","dağılım dengeli"))</f>
-        <v>T3: En yüksek maliyetli ürün toplamın %51 | yoğunlaşma yüksek, tek ürüne bağımlılık var</v>
+        <v>T3: En yüksek maliyetli ürün toplamın %17 | dağılım dengeli</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="24" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B46" s="26" t="n">
         <f aca="false">modulT4DonemFark</f>
-        <v>-905655762412412</v>
+        <v>-2714097916370430</v>
       </c>
       <c r="C46" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T4: Kur dönem farkı "&amp;TEXT(modulT4DonemFark,"#,##0")&amp;" ₺",IF(ABS(modulT4DonemFark)&gt;ToplamDepoTeslimMaliyeti*MutabakatEsikOran,"kur etkisi yüksek, maliyet duyarlı","kur etkisi kabul edilebilir"))</f>
-        <v>T4: Kur dönem farkı -905.655.762.412.412 ₺ | kur etkisi yüksek, maliyet duyarlı</v>
+        <v>T4: Kur dönem farkı -2.714.097.916.370.435 ₺ | kur etkisi yüksek, maliyet duyarlı</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="24" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B47" s="26" t="n">
         <f aca="false">modulT5MutabakatFark</f>
@@ -44453,7 +47506,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="24" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B48" s="28" t="n">
         <f aca="false">modulT6VergiYukOran</f>
@@ -44466,72 +47519,72 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="24" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B49" s="28" t="n">
         <f aca="false">modulO1AnomaliOran</f>
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="C49" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O1: Uç birim maliyetli ürün oranı %"&amp;TEXT(modulO1AnomaliOran*100,"0.0")&amp;"",IF(modulO1AnomaliOran&gt;0,"anomali ürünler tespit edildi, maliyetleri denetleyin","anomali yok"))</f>
-        <v>O1: Uç birim maliyetli ürün oranı %00 | anomali yok</v>
+        <v>O1: Uç birim maliyetli ürün oranı %08 | anomali ürünler tespit edildi, maliyetleri denetleyin</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="24" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B50" s="26" t="n">
         <f aca="false">modulO2TornadoZirve</f>
-        <v>517517.58</v>
+        <v>1550913.0995</v>
       </c>
       <c r="C50" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Tornado zirve etki "&amp;TEXT(modulO2TornadoZirve,"#,##0")&amp;" ₺",IF(modulO2TornadoZirve&gt;ToplamDepoTeslimMaliyeti*SenaryoEtkiEsik,"maliyet duyarlılığı yüksek, kur/vergi kritik","duyarlılık düşük"))</f>
-        <v>O2: Tornado zirve etki 517.518 ₺ | maliyet duyarlılığı yüksek, kur/vergi kritik</v>
+        <v>O2: Tornado zirve etki 1.550.913 ₺ | maliyet duyarlılığı yüksek, kur/vergi kritik</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="24" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B51" s="26" t="n">
         <f aca="false">modulO3SenaryoFark</f>
-        <v>258758.79</v>
+        <v>775456.54975</v>
       </c>
       <c r="C51" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O3: Kötümser-baz fark "&amp;TEXT(modulO3SenaryoFark,"#,##0")&amp;" ₺",IF(modulO3SenaryoFark&gt;ToplamDepoTeslimMaliyeti*SenaryoEtkiEsik,"kötümser senaryoda maliyet yükseliyor","senaryo aralığı kabul edilebilir"))</f>
-        <v>O3: Kötümser-baz fark 258.759 ₺ | senaryo aralığı kabul edilebilir</v>
+        <v>O3: Kötümser-baz fark 775.457 ₺ | senaryo aralığı kabul edilebilir</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B52" s="27" t="n">
         <f aca="false">modulO4NakitEtkiOran</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
       <c r="C52" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O4: Her 1 TL FOB için depo teslim maliyeti "&amp;TEXT(modulO4NakitEtkiOran,"0.00")&amp;" TL",IF(modulO4NakitEtkiOran&gt;1+VergiYukEsik,"maliyet çarpanı yüksek, nakit yükü artıyor","maliyet çarpanı kabul edilebilir"))</f>
-        <v>O4: Her 1 TL FOB için depo teslim maliyeti 1,48 TL | maliyet çarpanı yüksek, nakit yükü artıyor</v>
+        <v>O4: Her 1 TL FOB için depo teslim maliyeti 1,47 TL | maliyet çarpanı yüksek, nakit yükü artıyor</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="24" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B53" s="25" t="n">
         <f aca="false">modulO6MaliyetHhi</f>
-        <v>0.367760197416171</v>
+        <v>0.109119788636602</v>
       </c>
       <c r="C53" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O6: FOB yoğunlaşma endeksi "&amp;TEXT(modulO6MaliyetHhi,"0.00")&amp;"",IF(modulO6MaliyetHhi&gt;HhiYuksekEsik,"yoğunlaşma yüksek","dağılım dengeli"))</f>
-        <v>O6: FOB yoğunlaşma endeksi 0,37 | dağılım dengeli</v>
+        <v>O6: FOB yoğunlaşma endeksi 0,11 | dağılım dengeli</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="24" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B54" s="25" t="n">
         <f aca="false">modulO8KaliteSkoru</f>
@@ -44544,59 +47597,59 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="24" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B55" s="26" t="n">
         <f aca="false">modulI1MaliyetTahmin</f>
-        <v>619954.389669782</v>
+        <v>668002.446532015</v>
       </c>
       <c r="C55" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I1: Sonraki adet adımında beklenen maliyet "&amp;TEXT(modulI1MaliyetTahmin,"#,##0")&amp;" ₺",IF(modulI1MaliyetTahmin&gt;ToplamDepoTeslimMaliyeti*OrtalamaKur*0.2,"tahmin yüksek, ölçek etkisini gözden geçirin","tahmin sınır içinde"))</f>
-        <v>I1: Sonraki adet adımında beklenen maliyet 619.954 ₺ | tahmin yüksek, ölçek etkisini gözden geçirin</v>
+        <v>I1: Sonraki adet adımında beklenen maliyet 668.002 ₺ | tahmin yüksek, ölçek etkisini gözden geçirin</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B56" s="26" t="n">
         <f aca="false">modulI2MaliyetP90</f>
-        <v>39156.7518361446</v>
+        <v>51263.5666684809</v>
       </c>
       <c r="C56" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I2: Birim maliyet P90 değeri "&amp;TEXT(modulI2MaliyetP90,"#,##0")&amp;" ₺",IF(modulI2MaliyetP90&gt;OrtalamaNetBirimMaliyet*2,"P90 maliyeti ortalamanın iki katı üzerinde","P90 dağılımı kabul edilebilir"))</f>
-        <v>I2: Birim maliyet P90 değeri 39.157 ₺ | P90 maliyeti ortalamanın iki katı üzerinde</v>
+        <v>I2: Birim maliyet P90 değeri 51.264 ₺ | P90 maliyeti ortalamanın iki katı üzerinde</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="24" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B57" s="26" t="n">
         <f aca="false">modulI3MaliyetNpv</f>
-        <v>2352352.63636364</v>
+        <v>7049604.99772727</v>
       </c>
       <c r="C57" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I3: Depo teslim maliyetinin NPV değeri "&amp;TEXT(modulI3MaliyetNpv,"#,##0")&amp;" ₺",IF(modulI3MaliyetNpv&gt;ToplamDepoTeslimMaliyeti*NpvEsikOran,"NPV maliyeti yüksek","NPV maliyeti kabul edilebilir"))</f>
-        <v>I3: Depo teslim maliyetinin NPV değeri 2.352.353 ₺ | NPV maliyeti yüksek</v>
+        <v>I3: Depo teslim maliyetinin NPV değeri 7.049.605 ₺ | NPV maliyeti yüksek</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="24" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B58" s="26" t="n">
         <f aca="false">modulI7NakitAcik</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
       <c r="C58" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I7: Nakit açığı köprüsü "&amp;TEXT(modulI7NakitAcik,"#,##0")&amp;" ₺",IF(modulI7NakitAcik&gt;0,"peşin vergi ödemesi nakit yükü yaratıyor","nakit yükü karşılanıyor"))</f>
-        <v>I7: Nakit açığı köprüsü 706.438 ₺ | peşin vergi ödemesi nakit yükü yaratıyor</v>
+        <v>I7: Nakit açığı köprüsü 2.139.812 ₺ | peşin vergi ödemesi nakit yükü yaratıyor</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
@@ -44703,7 +47756,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -44737,32 +47790,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B5" s="30" t="n">
         <f aca="false">IFERROR(COUNTA(tblUrun[Ürün Adı]),0)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B6" s="30" t="n">
         <f aca="false">IFERROR(COUNTA(tblMasraf[Masraf Kalemi]),0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B7" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblUrun[Adet],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -44771,7 +47824,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B8" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblUrun[FOB Birim Fiyat (Döviz)],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -44780,7 +47833,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B9" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblUrun[Kur (₺)],"=0")&gt;0,"FAIL","PASS")</f>
@@ -44789,7 +47842,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="B10" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblUrun[Kur (₺)],"")&gt;0,"FAIL","PASS")</f>
@@ -44798,7 +47851,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="B11" s="30" t="str">
         <f aca="false">IF(SUMPRODUCT(--(tblUrun[Gümrük Vergisi Oranı]&gt;1))+SUMPRODUCT(--(tblUrun[Gümrük Vergisi Oranı]&lt;0))&gt;0,"FAIL","PASS")</f>
@@ -44807,7 +47860,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="B12" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblMasraf[Tutar TL],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -44816,12 +47869,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B16" s="32" t="n">
         <f aca="false">COUNTIF(B5:B12,"PASS")</f>
@@ -44830,7 +47883,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">COUNTIF(B5:B12,"FAIL")</f>
@@ -44839,7 +47892,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">COUNTIF(B5:B12,"WARN")</f>
@@ -44848,7 +47901,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">IFERROR(IF(DoluGirisHucre=0,0,MAX(0,VeriKaliteTaban-FAIL_Sayisi*VeriKaliteFailCeza-WARN_Sayisi*VeriKaliteUyariCeza)),0)</f>
@@ -44857,7 +47910,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B20" s="30" t="str">
         <f aca="false">IF(VeriKaliteSkoru&gt;=VeriKaliteIyiEsik,"İYİ",IF(VeriKaliteSkoru&gt;=VeriKaliteOrtaEsik,"ORTA","DÜŞÜK"))</f>
@@ -44866,16 +47919,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="B21" s="32" t="n">
         <f aca="false">IFERROR(COUNTA(tblUrun[Ürün Adı])+COUNTA(tblMasraf[Masraf Kalemi]),0)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">IFERROR(ROWS(tblUrun)+ROWS(tblMasraf),0)</f>
@@ -44884,16 +47937,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B23" s="33" t="n">
         <f aca="false">IFERROR(DoluGirisHucre/KayitKapasite,0)</f>
-        <v>0.00265957446808511</v>
+        <v>0.00731382978723404</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="B24" s="31" t="str">
         <f aca="false">IF(FAIL_Sayisi=0,"SAĞLIKLI","İNCELE")</f>
@@ -44902,7 +47955,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -45006,7 +48059,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -45040,35 +48093,35 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B6" s="26" t="n">
         <f aca="false">ToplamDepoTeslimMaliyeti</f>
-        <v>2587587.9</v>
+        <v>7754565.4975</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">MaliyetFaktoru</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">VergiYukOrani</f>
@@ -45077,7 +48130,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">modulT5MutabakatFark</f>
@@ -45086,7 +48139,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="B11" s="34" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(OR(MaliyetFaktoru&lt;1,ToplamFOB&lt;0),"DURDUR",IF(OR(VergiYukOrani&gt;VergiYukEsik,MaliyetFaktoru&gt;MaliyetFaktorEsik),"DURDUR",IF(OR(ABS(modulT5MutabakatFark)&gt;ToplamYurtIciMasraf*MutabakatEsikOran,AnomaliUrunAdedi&gt;0,modulI7NakitAcik&gt;0),"İNCELE","UYGUN"))))</f>
@@ -45095,7 +48148,7 @@
     </row>
     <row r="12" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="B12" s="35" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(MaliyetFaktoru&lt;1,"Maliyet faktörü 1 altında: FOB ve kur girişlerini kontrol edin.",IF(VergiYukOrani&gt;VergiYukEsik,"Vergi yükü oranı %"&amp;TEXT(VergiYukOrani,"0.0%")&amp;" eşiği aşıyor; vergi matrahı ve oranları gözden geçirin.",IF(MaliyetFaktoru&gt;MaliyetFaktorEsik,"Maliyet faktörü "&amp;TEXT(MaliyetFaktoru,"0.00")&amp;" eşiği aşıyor; yüksek kaldıraçlı ithalat.",IF(ABS(modulT5MutabakatFark)&gt;ToplamYurtIciMasraf*MutabakatEsikOran,"Yurt içi masraf dağıtımı ile masraf tablosu farklı; dağıtımı denetleyin.","Depo teslim maliyeti eşikler içinde; maliyet ürünlere dağıtıldı.")))))</f>
@@ -45104,7 +48157,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45126,7 +48179,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="str">
         <f aca="false">IF(AnomaliUrunAdedi&gt;0,"Uç birim maliyetli ürünlerin FOB ve oran girişlerini inceleyin","Birim maliyet dağılımı tutarlı")</f>
-        <v>Birim maliyet dağılımı tutarlı</v>
+        <v>Uç birim maliyetli ürünlerin FOB ve oran girişlerini inceleyin</v>
       </c>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
@@ -45134,14 +48187,14 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="str">
         <f aca="false">IF(modulI7NakitAcik&gt;0,"Peşin ödenen ithal vergileri nakit açığı "&amp;TEXT(modulI7NakitAcik,"#,##0")&amp;" ₺; kısa vadeli nakit planı yapın","İthal vergileri nakit yükü karşılanıyor")</f>
-        <v>Peşin ödenen ithal vergileri nakit açığı 706.438 ₺; kısa vadeli nakit planı yapın</v>
+        <v>Peşin ödenen ithal vergileri nakit açığı 2.139.812 ₺; kısa vadeli nakit planı yapın</v>
       </c>
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -45246,7 +48299,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -45280,36 +48333,36 @@
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B5" s="38"/>
       <c r="D5" s="39" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="E5" s="39"/>
       <c r="G5" s="40" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="H5" s="40"/>
       <c r="J5" s="41" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="K5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="n">
         <f aca="false">ToplamDepoTeslimMaliyeti</f>
-        <v>2587587.9</v>
+        <v>7754565.4975</v>
       </c>
       <c r="B6" s="42"/>
       <c r="D6" s="43" t="n">
         <f aca="false">MaliyetFaktoru</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
       <c r="E6" s="43"/>
       <c r="G6" s="44" t="n">
@@ -45325,61 +48378,61 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B8" s="26" t="n">
         <f aca="false">ToplamFOB</f>
-        <v>1743000</v>
+        <v>5279575</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="46" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">ToplamCIF</f>
-        <v>1830150</v>
+        <v>5543553.75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">ToplamVergi</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">ToplamYurtIciMasraf</f>
-        <v>51000</v>
+        <v>71200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">ToplamAdet</f>
-        <v>3275</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">OrtalamaNetBirimMaliyet</f>
-        <v>15241.0486097892</v>
+        <v>17633.2035335719</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">VeriKaliteSkoru</f>
@@ -45388,14 +48441,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="47" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B16" s="47"/>
       <c r="C16" s="47"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B17" s="46" t="str">
         <f aca="false">KararSonuc</f>
@@ -45412,7 +48465,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="47" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
@@ -45420,7 +48473,7 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"Veri yok","1. Maliyet faktörü "&amp;TEXT(MaliyetFaktoru,"0.00")&amp;" — her 1 TL FOB için depoya teslimde "&amp;TEXT(MaliyetFaktoru,"0.00")&amp;" TL")</f>
-        <v>1. Maliyet faktörü 1,48 — her 1 TL FOB için depoya teslimde 1,48 TL</v>
+        <v>1. Maliyet faktörü 1,47 — her 1 TL FOB için depoya teslimde 1,47 TL</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
@@ -45443,7 +48496,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="46" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45452,35 +48505,35 @@
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">ToplamFOB</f>
-        <v>1743000</v>
+        <v>5279575</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B26" s="48" t="n">
         <f aca="false">ToplamVergi</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B27" s="48" t="n">
         <f aca="false">ToplamYurtIciMasraf</f>
-        <v>51000</v>
+        <v>71200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="46" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B30" s="33" t="n">
         <f aca="false">IFERROR(ToplamGumrukVergisi/MAX(BolumPaydaTaban,ToplamVergi),0)</f>
@@ -45489,7 +48542,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="B31" s="33" t="n">
         <f aca="false">IFERROR(ToplamOtv/MAX(BolumPaydaTaban,ToplamVergi),0)</f>
@@ -45498,7 +48551,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B32" s="33" t="n">
         <f aca="false">IFERROR(ToplamKdv/MAX(BolumPaydaTaban,ToplamVergi),0)</f>
@@ -45507,7 +48560,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="46" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45517,7 +48570,7 @@
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Maliyet Faktörü],ROW()-ROW($A$34)),0)</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45527,7 +48580,7 @@
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Maliyet Faktörü],ROW()-ROW($A$34)),0)</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45537,7 +48590,7 @@
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Maliyet Faktörü],ROW()-ROW($A$34)),0)</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45547,63 +48600,63 @@
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Maliyet Faktörü],ROW()-ROW($A$34)),0)</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="46" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B41" s="48" t="n">
         <f aca="false">OrtalamaNetBirimMaliyet</f>
-        <v>15241.0486097892</v>
+        <v>17633.2035335719</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="B42" s="48" t="n">
         <f aca="false">modulI2MaliyetP90</f>
-        <v>39156.7518361446</v>
+        <v>51263.5666684809</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="46" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B45" s="48" t="n">
         <f aca="false">IFERROR(SenaryoMaliyetKotumser-ToplamDepoTeslimMaliyeti,0)</f>
-        <v>258758.79</v>
+        <v>775456.54975</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B46" s="48" t="n">
         <f aca="false">IFERROR(ToplamDepoTeslimMaliyeti-SenaryoMaliyetIyimser,0)</f>
-        <v>258758.79</v>
+        <v>775456.54975</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="46" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="31" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B49" s="33" t="n">
         <f aca="false">IFERROR(ToplamVergi/MAX(BolumPaydaTaban,ToplamFOB),0)</f>
@@ -45612,16 +48665,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="31" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B50" s="48" t="n">
         <f aca="false">modulI7NakitAcik</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
@@ -45743,7 +48796,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -45777,43 +48830,43 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">IFERROR(ToplamDepoTeslimMaliyeti*(1+SenaryoKotumserKat),0)</f>
-        <v>2846346.69</v>
+        <v>8530022.04725</v>
       </c>
       <c r="C7" s="26" t="n">
         <f aca="false">ToplamDepoTeslimMaliyeti</f>
-        <v>2587587.9</v>
+        <v>7754565.4975</v>
       </c>
       <c r="D7" s="26" t="n">
         <f aca="false">IFERROR(ToplamDepoTeslimMaliyeti*(1-SenaryoIyimserKat),0)</f>
-        <v>2328829.11</v>
+        <v>6979108.94775</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">IFERROR(VergiYukOrani*(1+SenaryoKotumserKat),0)</f>
@@ -45830,41 +48883,41 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">IFERROR(MaliyetFaktoru*(1+SenaryoKotumserKat),0)</f>
-        <v>1.63301588640275</v>
+        <v>1.61566452740041</v>
       </c>
       <c r="C9" s="27" t="n">
         <f aca="false">MaliyetFaktoru</f>
-        <v>1.48455989672978</v>
+        <v>1.46878593400037</v>
       </c>
       <c r="D9" s="27" t="n">
         <f aca="false">IFERROR(MaliyetFaktoru*(1-SenaryoIyimserKat),0)</f>
-        <v>1.3361039070568</v>
+        <v>1.32190734060033</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamVergi*(1+SenaryoKotumserKat)-PesinOdemeTutari),0)</f>
-        <v>777081.69</v>
+        <v>2353792.92225</v>
       </c>
       <c r="C10" s="26" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamVergi-PesinOdemeTutari),0)</f>
-        <v>706437.9</v>
+        <v>2139811.7475</v>
       </c>
       <c r="D10" s="26" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamVergi*(1-SenaryoIyimserKat)-PesinOdemeTutari),0)</f>
-        <v>635794.11</v>
+        <v>1925830.57275</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B11" s="30" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(B8&gt;VergiYukEsik,"DURDUR",IF(OR(B10&gt;0,B9&gt;MaliyetFaktorEsik),"İNCELE","UYGUN")))</f>
@@ -45881,12 +48934,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B14" s="50" t="n">
         <f aca="false">IFERROR(OrtalamaKur*(1-DuyarliDegisim),0)</f>
@@ -45903,11 +48956,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B15" s="48" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamFOB*(1+DuyarliDegisim)*MaliyetFaktoru-ToplamDepoTeslimMaliyeti),0)</f>
-        <v>129379.395</v>
+        <v>387728.274875</v>
       </c>
       <c r="C15" s="48" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamFOB*MaliyetFaktoru-ToplamDepoTeslimMaliyeti),0)</f>
@@ -45920,7 +48973,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="B17" s="31" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(MAX(B10,C10,D10)&gt;0,"NAKİT AÇIĞI VAR","NAKİT DENGELİ"))</f>
@@ -45929,7 +48982,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
